--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_apoyopot_a_2020_magallanes.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_apoyopot_a_2020_magallanes.xlsx
@@ -120,7 +120,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 14:15</t>
+    <t xml:space="preserve">2026-09-24 01:05</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -919,19 +919,19 @@
         <v>28</v>
       </c>
       <c r="C19" s="2" t="n">
-        <v>-0.55</v>
+        <v>-0.43</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>-0.32</v>
+        <v>-0.31</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>-0.23</v>
+        <v>-0.13</v>
       </c>
     </row>
     <row r="20">
@@ -942,19 +942,19 @@
         <v>28</v>
       </c>
       <c r="C20" s="2" t="n">
-        <v>0.32</v>
+        <v>0.23</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>0.19</v>
+        <v>0.17</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>0.13</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="21">
@@ -965,19 +965,19 @@
         <v>28</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>-0.43</v>
+        <v>-0.39</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E21" s="2" t="n">
         <v>-0.08</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>-0.35</v>
+        <v>-0.31</v>
       </c>
     </row>
   </sheetData>
